--- a/tame_output/ON/bt/strategyON_20231018.xlsx
+++ b/tame_output/ON/bt/strategyON_20231018.xlsx
@@ -595,17 +595,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.8%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -763,11 +763,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,12 +776,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.6%</t>
+          <t>100.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.0%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130.2%</t>
+          <t>130.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.7%</t>
+          <t>124.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1753"/>
+  <dimension ref="A1:G1754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41829,7 +41829,7 @@
         <v>45215</v>
       </c>
       <c r="B1753" t="n">
-        <v>2.856263949404791</v>
+        <v>2.855808668290733</v>
       </c>
       <c r="C1753" t="n">
         <v>2.959094075792072</v>
@@ -41845,6 +41845,29 @@
       </c>
       <c r="G1753" t="n">
         <v>4.256040226879542</v>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="2" t="n">
+        <v>45216</v>
+      </c>
+      <c r="B1754" t="n">
+        <v>2.863148958350867</v>
+      </c>
+      <c r="C1754" t="n">
+        <v>2.957874679524909</v>
+      </c>
+      <c r="D1754" t="n">
+        <v>1.567441496733527</v>
+      </c>
+      <c r="E1754" t="n">
+        <v>3.584494853904573</v>
+      </c>
+      <c r="F1754" t="n">
+        <v>2.162073444781766</v>
+      </c>
+      <c r="G1754" t="n">
+        <v>4.255118746393969</v>
       </c>
     </row>
   </sheetData>
